--- a/output/DASHBOARD.xlsx
+++ b/output/DASHBOARD.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:58:42</t>
+          <t>10:51:15</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>133 sec</t>
+          <t>158 sec</t>
         </is>
       </c>
     </row>

--- a/output/DASHBOARD.xlsx
+++ b/output/DASHBOARD.xlsx
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20.83 %</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:51:15</t>
+          <t>12:46:55</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>⚠ Metrics mismatch</t>
+          <t>✓ Metrics verified</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -778,7 +778,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>158 sec</t>
+          <t>28 sec</t>
         </is>
       </c>
     </row>
